--- a/artfynd/A 43000-2024 artfynd.xlsx
+++ b/artfynd/A 43000-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120848393</v>
+        <v>120848397</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>82385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>769840</v>
+        <v>769781</v>
       </c>
       <c r="R2" t="n">
-        <v>7208209</v>
+        <v>7208130</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120848390</v>
+        <v>120848391</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,12 +810,16 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769821</v>
+        <v>769808</v>
       </c>
       <c r="R3" t="n">
-        <v>7208189</v>
+        <v>7208161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120848397</v>
+        <v>120848396</v>
       </c>
       <c r="B4" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769781</v>
+        <v>769831</v>
       </c>
       <c r="R4" t="n">
-        <v>7208130</v>
+        <v>7208233</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120848388</v>
+        <v>120848398</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>82385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,42 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769825</v>
+        <v>769762</v>
       </c>
       <c r="R5" t="n">
-        <v>7208217</v>
+        <v>7208055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Då ringhack räknas som färska av SKS om de är yngre än 5 år rapporterar även jag det så. Jag har svårt att säga exakt hur gamla spåren är, men det känns rimligt att de inte är från ifjol, men inte heller +5 år gamla med tanke på t.ex. saven. Det finns dock ringhack i det större området som gjordes i våras.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120848395</v>
+        <v>120848388</v>
       </c>
       <c r="B6" t="n">
-        <v>82382</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,34 +1111,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769841</v>
+        <v>769825</v>
       </c>
       <c r="R6" t="n">
-        <v>7208216</v>
+        <v>7208217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Då ringhack räknas som färska av SKS om de är yngre än 5 år rapporterar även jag det så. Jag har svårt att säga exakt hur gamla spåren är, men det känns rimligt att de inte är från ifjol, men inte heller +5 år gamla med tanke på t.ex. saven. Det finns dock ringhack i det större området som gjordes i våras.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120848398</v>
+        <v>120848389</v>
       </c>
       <c r="B7" t="n">
-        <v>82382</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,34 +1226,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769762</v>
+        <v>769840</v>
       </c>
       <c r="R7" t="n">
-        <v>7208055</v>
+        <v>7208209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,6 +1298,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Letade mat lågt, del av ett messträck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120848389</v>
+        <v>120848395</v>
       </c>
       <c r="B8" t="n">
-        <v>57501</v>
+        <v>82385</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,46 +1345,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769840</v>
+        <v>769841</v>
       </c>
       <c r="R8" t="n">
-        <v>7208209</v>
+        <v>7208216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,11 +1405,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Letade mat lågt, del av ett messträck</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120848391</v>
+        <v>120848393</v>
       </c>
       <c r="B9" t="n">
-        <v>57501</v>
+        <v>90715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,46 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769808</v>
+        <v>769840</v>
       </c>
       <c r="R9" t="n">
-        <v>7208161</v>
+        <v>7208209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120848396</v>
+        <v>120848390</v>
       </c>
       <c r="B10" t="n">
-        <v>82382</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,34 +1549,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769831</v>
+        <v>769821</v>
       </c>
       <c r="R10" t="n">
-        <v>7208233</v>
+        <v>7208189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 43000-2024 artfynd.xlsx
+++ b/artfynd/A 43000-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120848391</v>
+        <v>120848390</v>
       </c>
       <c r="B3" t="n">
         <v>57504</v>
@@ -810,16 +810,12 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769808</v>
+        <v>769821</v>
       </c>
       <c r="R3" t="n">
-        <v>7208161</v>
+        <v>7208189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120848396</v>
+        <v>120848393</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>90715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769831</v>
+        <v>769840</v>
       </c>
       <c r="R4" t="n">
-        <v>7208233</v>
+        <v>7208209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120848398</v>
+        <v>120848395</v>
       </c>
       <c r="B5" t="n">
         <v>82385</v>
@@ -1033,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769762</v>
+        <v>769841</v>
       </c>
       <c r="R5" t="n">
-        <v>7208055</v>
+        <v>7208216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120848388</v>
+        <v>120848398</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,42 +1107,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769825</v>
+        <v>769762</v>
       </c>
       <c r="R6" t="n">
-        <v>7208217</v>
+        <v>7208055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1167,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Då ringhack räknas som färska av SKS om de är yngre än 5 år rapporterar även jag det så. Jag har svårt att säga exakt hur gamla spåren är, men det känns rimligt att de inte är från ifjol, men inte heller +5 år gamla med tanke på t.ex. saven. Det finns dock ringhack i det större området som gjordes i våras.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120848395</v>
+        <v>120848391</v>
       </c>
       <c r="B8" t="n">
-        <v>82385</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,34 +1328,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Åliden, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769841</v>
+        <v>769808</v>
       </c>
       <c r="R8" t="n">
-        <v>7208216</v>
+        <v>7208161</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120848393</v>
+        <v>120848396</v>
       </c>
       <c r="B9" t="n">
-        <v>90715</v>
+        <v>82385</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769840</v>
+        <v>769831</v>
       </c>
       <c r="R9" t="n">
-        <v>7208209</v>
+        <v>7208233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120848390</v>
+        <v>120848388</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,7 +1566,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1581,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769821</v>
+        <v>769825</v>
       </c>
       <c r="R10" t="n">
-        <v>7208189</v>
+        <v>7208217</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,6 +1612,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Då ringhack räknas som färska av SKS om de är yngre än 5 år rapporterar även jag det så. Jag har svårt att säga exakt hur gamla spåren är, men det känns rimligt att de inte är från ifjol, men inte heller +5 år gamla med tanke på t.ex. saven. Det finns dock ringhack i det större området som gjordes i våras.</t>
         </is>
       </c>
       <c r="AD10" t="b">
